--- a/docs/public/sprints/sprint-3/3_Retorno_Economico.xlsx
+++ b/docs/public/sprints/sprint-3/3_Retorno_Economico.xlsx
@@ -122,19 +122,19 @@
     <t xml:space="preserve">CAPEX — investimento inicial</t>
   </si>
   <si>
-    <t xml:space="preserve">Planilha 2 · aba Orçamento · aprimoramento e implantação</t>
+    <t xml:space="preserve">Planilha 2 · produtização (2,5 meses) + pentest e revisão de segurança</t>
   </si>
   <si>
     <t xml:space="preserve">OPEX fixo anual</t>
   </si>
   <si>
-    <t xml:space="preserve">Planilha 2 · Vercel + Red Hat + sustentação</t>
+    <t xml:space="preserve">Planilha 2 · clusters, Azure compute, Vercel, observabilidade, suporte, sustentação, retreinamento</t>
   </si>
   <si>
     <t xml:space="preserve">OPEX variável anual</t>
   </si>
   <si>
-    <t xml:space="preserve">Planilha 2 · reserva do Azure SQL Database</t>
+    <t xml:space="preserve">Planilha 2 · armazenamento e backup do Azure SQL, que escalam com o volume</t>
   </si>
   <si>
     <t xml:space="preserve">OPEX total anual</t>
@@ -323,16 +323,16 @@
     <t xml:space="preserve">Payback (meses)</t>
   </si>
   <si>
-    <t xml:space="preserve">O índice de margem de contribuição supera 98% em todas as faixas: o custo variável de R$ 2,84 por porta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ao ano é desprezível diante de qualquer economia unitária plausível. É um projeto essencialmente de custo fixo.</t>
+    <t xml:space="preserve">O custo variável é de R$ 24,34 por porta ao ano. O índice de margem de contribuição permanece alto:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o projeto é essencialmente de custo fixo, e a escala de 528 portas dilui o componente variável.</t>
   </si>
   <si>
     <t xml:space="preserve">2. Sensibilidade ao custo dos alertas improdutivos (Cf)</t>
   </si>
   <si>
-    <t xml:space="preserve">Assumindo E = R$ 1.000 por falha evitada. O projeto deixa de gerar economia líquida quando E &lt; 2,33 × Cf.</t>
+    <t xml:space="preserve">Assumindo E = R$ 2.000 por falha evitada. O projeto deixa de gerar economia líquida quando E &lt; 2,33 × Cf.</t>
   </si>
   <si>
     <t xml:space="preserve">Cf (R$/alerta)</t>
@@ -1151,7 +1151,7 @@
         <v>32</v>
       </c>
       <c r="B26" s="13" t="n">
-        <v>18000</v>
+        <v>85000</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>33</v>
@@ -1162,7 +1162,7 @@
         <v>34</v>
       </c>
       <c r="B27" s="13" t="n">
-        <v>11015.1</v>
+        <v>251355.51</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>35</v>
@@ -1173,7 +1173,7 @@
         <v>36</v>
       </c>
       <c r="B28" s="13" t="n">
-        <v>1500</v>
+        <v>12852</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>37</v>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="B29" s="14" t="n">
         <f aca="false">B27+B28</f>
-        <v>12515.1</v>
+        <v>264207.51</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B30" s="16" t="n">
         <f aca="false">B26+B29</f>
-        <v>30515.1</v>
+        <v>349207.51</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B31" s="14" t="n">
         <f aca="false">B28/B10</f>
-        <v>2.84090909090909</v>
+        <v>24.3409090909091</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="B63" s="16" t="n">
         <f aca="false">B30/B44</f>
-        <v>30.2729166666667</v>
+        <v>346.436021825397</v>
       </c>
       <c r="C63" s="9" t="s">
         <v>84</v>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="B64" s="16" t="n">
         <f aca="false">B29/B44</f>
-        <v>12.4157738095238</v>
+        <v>262.110625</v>
       </c>
       <c r="C64" s="9" t="s">
         <v>84</v>
@@ -1607,167 +1607,167 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="B7" s="14" t="n">
         <f aca="false">A7*Modelo!$B$44</f>
-        <v>100800</v>
+        <v>504000</v>
       </c>
       <c r="C7" s="14" t="n">
         <f aca="false">B7/Modelo!$B$10</f>
-        <v>190.909090909091</v>
+        <v>954.545454545455</v>
       </c>
       <c r="D7" s="14" t="n">
         <f aca="false">C7-Modelo!$B$31</f>
-        <v>188.068181818182</v>
+        <v>930.204545454545</v>
       </c>
       <c r="E7" s="11" t="n">
         <f aca="false">Modelo!$B$27/D7</f>
-        <v>58.5697160120846</v>
+        <v>270.215310415598</v>
       </c>
       <c r="F7" s="14" t="n">
         <f aca="false">B7-Modelo!$B$29</f>
-        <v>88284.9</v>
+        <v>239792.49</v>
       </c>
       <c r="G7" s="18" t="n">
         <f aca="false">(F7-Modelo!$B$26)/Modelo!$B$26</f>
-        <v>3.90471666666667</v>
+        <v>1.82108811764706</v>
       </c>
       <c r="H7" s="11" t="n">
         <f aca="false">Modelo!$B$26/F7*12</f>
-        <v>2.44662450770177</v>
+        <v>4.25367783619912</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="B8" s="14" t="n">
         <f aca="false">A8*Modelo!$B$44</f>
-        <v>302400</v>
+        <v>1008000</v>
       </c>
       <c r="C8" s="14" t="n">
         <f aca="false">B8/Modelo!$B$10</f>
-        <v>572.727272727273</v>
+        <v>1909.09090909091</v>
       </c>
       <c r="D8" s="14" t="n">
         <f aca="false">C8-Modelo!$B$31</f>
-        <v>569.886363636364</v>
+        <v>1884.75</v>
       </c>
       <c r="E8" s="11" t="n">
         <f aca="false">Modelo!$B$27/D8</f>
-        <v>19.3285902293121</v>
+        <v>133.36278551532</v>
       </c>
       <c r="F8" s="14" t="n">
         <f aca="false">B8-Modelo!$B$29</f>
-        <v>289884.9</v>
+        <v>743792.49</v>
       </c>
       <c r="G8" s="18" t="n">
         <f aca="false">(F8-Modelo!$B$26)/Modelo!$B$26</f>
-        <v>15.1047166666667</v>
+        <v>7.75049988235294</v>
       </c>
       <c r="H8" s="11" t="n">
         <f aca="false">Modelo!$B$26/F8*12</f>
-        <v>0.745123323084438</v>
+        <v>1.37135022699678</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="B9" s="14" t="n">
         <f aca="false">A9*Modelo!$B$44</f>
-        <v>504000</v>
+        <v>2016000</v>
       </c>
       <c r="C9" s="14" t="n">
         <f aca="false">B9/Modelo!$B$10</f>
-        <v>954.545454545455</v>
+        <v>3818.18181818182</v>
       </c>
       <c r="D9" s="14" t="n">
         <f aca="false">C9-Modelo!$B$31</f>
-        <v>951.704545454545</v>
+        <v>3793.84090909091</v>
       </c>
       <c r="E9" s="11" t="n">
         <f aca="false">Modelo!$B$27/D9</f>
-        <v>11.5740752238806</v>
+        <v>66.25357151843</v>
       </c>
       <c r="F9" s="14" t="n">
         <f aca="false">B9-Modelo!$B$29</f>
-        <v>491484.9</v>
+        <v>1751792.49</v>
       </c>
       <c r="G9" s="18" t="n">
         <f aca="false">(F9-Modelo!$B$26)/Modelo!$B$26</f>
-        <v>26.3047166666667</v>
+        <v>19.6093234117647</v>
       </c>
       <c r="H9" s="11" t="n">
         <f aca="false">Modelo!$B$26/F9*12</f>
-        <v>0.439484509086647</v>
+        <v>0.582260744821437</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="B10" s="14" t="n">
         <f aca="false">A10*Modelo!$B$44</f>
-        <v>1008000</v>
+        <v>3024000</v>
       </c>
       <c r="C10" s="14" t="n">
         <f aca="false">B10/Modelo!$B$10</f>
-        <v>1909.09090909091</v>
+        <v>5727.27272727273</v>
       </c>
       <c r="D10" s="14" t="n">
         <f aca="false">C10-Modelo!$B$31</f>
-        <v>1906.25</v>
+        <v>5702.93181818182</v>
       </c>
       <c r="E10" s="11" t="n">
         <f aca="false">Modelo!$B$27/D10</f>
-        <v>5.7784131147541</v>
+        <v>44.0747878483555</v>
       </c>
       <c r="F10" s="14" t="n">
         <f aca="false">B10-Modelo!$B$29</f>
-        <v>995484.9</v>
+        <v>2759792.49</v>
       </c>
       <c r="G10" s="18" t="n">
         <f aca="false">(F10-Modelo!$B$26)/Modelo!$B$26</f>
-        <v>54.3047166666667</v>
+        <v>31.4681469411765</v>
       </c>
       <c r="H10" s="11" t="n">
         <f aca="false">Modelo!$B$26/F10*12</f>
-        <v>0.216979684975633</v>
+        <v>0.369593005161051</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="n">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="B11" s="14" t="n">
         <f aca="false">A11*Modelo!$B$44</f>
-        <v>2016000</v>
+        <v>5040000</v>
       </c>
       <c r="C11" s="14" t="n">
         <f aca="false">B11/Modelo!$B$10</f>
-        <v>3818.18181818182</v>
+        <v>9545.45454545455</v>
       </c>
       <c r="D11" s="14" t="n">
         <f aca="false">C11-Modelo!$B$31</f>
-        <v>3815.34090909091</v>
+        <v>9521.11363636364</v>
       </c>
       <c r="E11" s="11" t="n">
         <f aca="false">Modelo!$B$27/D11</f>
-        <v>2.88705524944155</v>
+        <v>26.3998014938092</v>
       </c>
       <c r="F11" s="14" t="n">
         <f aca="false">B11-Modelo!$B$29</f>
-        <v>2003484.9</v>
+        <v>4775792.49</v>
       </c>
       <c r="G11" s="18" t="n">
         <f aca="false">(F11-Modelo!$B$26)/Modelo!$B$26</f>
-        <v>110.304716666667</v>
+        <v>55.185794</v>
       </c>
       <c r="H11" s="11" t="n">
         <f aca="false">Modelo!$B$26/F11*12</f>
-        <v>0.107812142731897</v>
+        <v>0.213577118799816</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1824,8 +1824,8 @@
         <v>0</v>
       </c>
       <c r="B19" s="14" t="n">
-        <f aca="false">1000*Modelo!$B$44</f>
-        <v>1008000</v>
+        <f aca="false">2000*Modelo!$B$44</f>
+        <v>2016000</v>
       </c>
       <c r="C19" s="14" t="n">
         <f aca="false">A19*Modelo!$B$20</f>
@@ -1833,11 +1833,11 @@
       </c>
       <c r="D19" s="14" t="n">
         <f aca="false">B19-C19</f>
-        <v>1008000</v>
+        <v>2016000</v>
       </c>
       <c r="E19" s="14" t="n">
         <f aca="false">D19-Modelo!$B$29</f>
-        <v>995484.9</v>
+        <v>1751792.49</v>
       </c>
       <c r="F19" s="22" t="str">
         <f aca="false">IF(E19&gt;0,"Viável","Inviável")</f>
@@ -1846,23 +1846,23 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="B20" s="14" t="n">
-        <f aca="false">1000*Modelo!$B$44</f>
-        <v>1008000</v>
+        <f aca="false">2000*Modelo!$B$44</f>
+        <v>2016000</v>
       </c>
       <c r="C20" s="14" t="n">
         <f aca="false">A20*Modelo!$B$20</f>
-        <v>235200</v>
+        <v>470400</v>
       </c>
       <c r="D20" s="14" t="n">
         <f aca="false">B20-C20</f>
-        <v>772800</v>
+        <v>1545600</v>
       </c>
       <c r="E20" s="14" t="n">
         <f aca="false">D20-Modelo!$B$29</f>
-        <v>760284.9</v>
+        <v>1281392.49</v>
       </c>
       <c r="F20" s="22" t="str">
         <f aca="false">IF(E20&gt;0,"Viável","Inviável")</f>
@@ -1871,23 +1871,23 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="B21" s="14" t="n">
-        <f aca="false">1000*Modelo!$B$44</f>
-        <v>1008000</v>
+        <f aca="false">2000*Modelo!$B$44</f>
+        <v>2016000</v>
       </c>
       <c r="C21" s="14" t="n">
         <f aca="false">A21*Modelo!$B$20</f>
-        <v>470400</v>
+        <v>940800</v>
       </c>
       <c r="D21" s="14" t="n">
         <f aca="false">B21-C21</f>
-        <v>537600</v>
+        <v>1075200</v>
       </c>
       <c r="E21" s="14" t="n">
         <f aca="false">D21-Modelo!$B$29</f>
-        <v>525084.9</v>
+        <v>810992.49</v>
       </c>
       <c r="F21" s="22" t="str">
         <f aca="false">IF(E21&gt;0,"Viável","Inviável")</f>
@@ -1896,23 +1896,23 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="B22" s="14" t="n">
-        <f aca="false">1000*Modelo!$B$44</f>
-        <v>1008000</v>
+        <f aca="false">2000*Modelo!$B$44</f>
+        <v>2016000</v>
       </c>
       <c r="C22" s="14" t="n">
         <f aca="false">A22*Modelo!$B$20</f>
-        <v>705600</v>
+        <v>1411200</v>
       </c>
       <c r="D22" s="14" t="n">
         <f aca="false">B22-C22</f>
-        <v>302400</v>
+        <v>604800</v>
       </c>
       <c r="E22" s="14" t="n">
         <f aca="false">D22-Modelo!$B$29</f>
-        <v>289884.9</v>
+        <v>340592.49</v>
       </c>
       <c r="F22" s="22" t="str">
         <f aca="false">IF(E22&gt;0,"Viável","Inviável")</f>
@@ -1921,23 +1921,23 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="n">
-        <v>429</v>
+        <v>857</v>
       </c>
       <c r="B23" s="14" t="n">
-        <f aca="false">1000*Modelo!$B$44</f>
-        <v>1008000</v>
+        <f aca="false">2000*Modelo!$B$44</f>
+        <v>2016000</v>
       </c>
       <c r="C23" s="14" t="n">
         <f aca="false">A23*Modelo!$B$20</f>
-        <v>1009008</v>
+        <v>2015664</v>
       </c>
       <c r="D23" s="14" t="n">
         <f aca="false">B23-C23</f>
-        <v>-1008</v>
+        <v>336</v>
       </c>
       <c r="E23" s="14" t="n">
         <f aca="false">D23-Modelo!$B$29</f>
-        <v>-13523.1</v>
+        <v>-263871.51</v>
       </c>
       <c r="F23" s="22" t="str">
         <f aca="false">IF(E23&gt;0,"Viável","Inviável")</f>
@@ -1946,23 +1946,23 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="B24" s="14" t="n">
-        <f aca="false">1000*Modelo!$B$44</f>
-        <v>1008000</v>
+        <f aca="false">2000*Modelo!$B$44</f>
+        <v>2016000</v>
       </c>
       <c r="C24" s="14" t="n">
         <f aca="false">A24*Modelo!$B$20</f>
-        <v>1176000</v>
+        <v>2352000</v>
       </c>
       <c r="D24" s="14" t="n">
         <f aca="false">B24-C24</f>
-        <v>-168000</v>
+        <v>-336000</v>
       </c>
       <c r="E24" s="14" t="n">
         <f aca="false">D24-Modelo!$B$29</f>
-        <v>-180515.1</v>
+        <v>-600207.51</v>
       </c>
       <c r="F24" s="22" t="str">
         <f aca="false">IF(E24&gt;0,"Viável","Inviável")</f>
@@ -2020,11 +2020,11 @@
       </c>
       <c r="D29" s="14" t="n">
         <f aca="false">Modelo!$B$30/B29</f>
-        <v>121.091666666667</v>
+        <v>1385.74408730159</v>
       </c>
       <c r="E29" s="14" t="n">
         <f aca="false">Modelo!$B$29/B29</f>
-        <v>49.6630952380952</v>
+        <v>1048.4425</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2041,11 +2041,11 @@
       </c>
       <c r="D30" s="14" t="n">
         <f aca="false">Modelo!$B$30/B30</f>
-        <v>60.5458333333333</v>
+        <v>692.872043650794</v>
       </c>
       <c r="E30" s="14" t="n">
         <f aca="false">Modelo!$B$29/B30</f>
-        <v>24.8315476190476</v>
+        <v>524.22125</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2062,11 +2062,11 @@
       </c>
       <c r="D31" s="14" t="n">
         <f aca="false">Modelo!$B$30/B31</f>
-        <v>40.3638888888889</v>
+        <v>461.914695767196</v>
       </c>
       <c r="E31" s="14" t="n">
         <f aca="false">Modelo!$B$29/B31</f>
-        <v>16.5543650793651</v>
+        <v>349.480833333333</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2083,11 +2083,11 @@
       </c>
       <c r="D32" s="14" t="n">
         <f aca="false">Modelo!$B$30/B32</f>
-        <v>30.2729166666667</v>
+        <v>346.436021825397</v>
       </c>
       <c r="E32" s="14" t="n">
         <f aca="false">Modelo!$B$29/B32</f>
-        <v>12.4157738095238</v>
+        <v>262.110625</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
